--- a/templates/000_pm_suite/02_프로젝트 개발/06_검수/02_통합테스트/프로젝트명_검수확인서_V1.0_20230530.xlsx
+++ b/templates/000_pm_suite/02_프로젝트 개발/06_검수/02_통합테스트/프로젝트명_검수확인서_V1.0_20230530.xlsx
@@ -529,7 +529,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-59] SyncGuard AI 통합테스트 완료 및 품질 검수 확인서 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-59] SyncFlow AI 통합테스트 완료 및 품질 검수 확인서 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>42스텝 업무 시나리오(SSO~OCR~AI심의~콜백) 100% 통과</t>
+          <t>42스텝 업무 시나리오(SSO~OCR~AI검증~콜백) 100% 통과</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>동시 200 VU 부하 시 단건 심의 평균 15초 이내, 에러율 0.1% 미만</t>
+          <t>동시 200 VU 부하 시 단건 검증 평균 15초 이내, 에러율 0.1% 미만</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>취약점 0건 (전성분 기밀 격리 완벽 검증)</t>
+          <t>취약점 0건 (자재BOM 기밀 격리 완벽 검증)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
